--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-007_申請詳細取得_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-007_申請詳細取得_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="9344025"/>
+    <ext cx="8572500" cy="9544050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-007 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-007 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="64" customHeight="1">
+    <row r="3" ht="169" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -1804,7 +1804,10 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：toIso の呼び出しを AppTime#toIso（ONL-002 定義）に変更、handleTypeMismatch の定義元を ONL-001 に統一、updated_at をトリガ自動更新に変更、認証なしを 401 / E-001 の JSON に更新</t>
+          <t>・確定設計変更 D1〜D10 を反映：toIso の呼び出しを AppTime#toIso（ONL-002 定義）に変更、handleTypeMismatch の定義元を ONL-001 に統一、updated_at をトリガ自動更新に変更、認証なしを 401 / E-001 の JSON に更新
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）
+・Integer 同士の比較は == ではなく equals を使用（stepNo と currentStep）
+・日付項目（startDate / endDate）は LocalDate のまま返し、Jackson が yyyy-MM-dd で出力する</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -3955,7 +3958,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>public RequestDetailResponse detail(@AuthenticationPrincipal Jwt jwt, @PathVariable Long id)</t>
+          <t>public RequestDetailResponse detail(Authentication auth, @PathVariable Long id)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -4018,17 +4021,17 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン（sub = users.id）</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -4096,7 +4099,7 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>1. Long viewerId = Long.valueOf(jwt.getSubject());
+          <t>1. Long viewerId = Long.valueOf(auth.getName());
 2. return requestService.getDetail(id, viewerId);</t>
         </is>
       </c>
@@ -4328,7 +4331,7 @@
 LeaveType type = r.getLeaveTypeId() == null ? null : leaveTypeRepository.findById(r.getLeaveTypeId()).orElse(null);
 BigDecimal balance = null;                                                    // ⑤
 if (RequestType.LEAVE.equals(r.getRequestType()) &amp;&amp; type != null &amp;&amp; "LIMITED".equals(type.getMaxDaysRule()))
-    balance = leaveBalanceService.getRemainingDays(r.getUserId(), type.getId(), LocalDate.now(JST));
+    balance = leaveBalanceService.getRemainingDays(r.getUserId(), type.getId(), LocalDate.now(clock));
 return new RequestDetailResponse(toDetail(r, applicant, dept, type), toSteps(r, steps, users), balance);   // ⑥</t>
         </is>
       </c>

--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-007_申請詳細取得_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-007_申請詳細取得_オンライン詳細設計書.xlsx
@@ -303,7 +303,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10953750" cy="9772650"/>
+    <ext cx="10953750" cy="10487025"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-007 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜026)の概要。本書はそのうち ONL-007 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1116,7 +1116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E28"/>
+  <dimension ref="A2:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1506,204 +1506,385 @@
       </c>
       <c r="E17" s="7" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="18" ht="49" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>WITHDRAWN の申請（2 段とも WAITING のまま）</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>steps[].status は両方 "SKIPPED"、current は両方 false。DB の値（WAITING）は変わらない</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>displayStatus</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="49" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>RETURNED（1 段目が差戻し RETURNED、2 段目は WAITING のまま）／REJECTED（1 段目が REJECTED、2 段目 WAITING）</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>1 段目は RETURNED / REJECTED のまま、2 段目は SKIPPED</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>処理済みのステップは変換しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="49" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>PENDING・current_step=1・1 段目 WAITING・2 段目 WAITING</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>1 段目 WAITING（current=true）、2 段目 WAITING（current=false。SKIPPED ではない）</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>PENDING の間は WAITING のまま</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>APPROVED の申請（全ステップ APPROVED）</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>status は APPROVED のまま、SKIPPED は出ない</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="79" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION の申請（corrected_break_kind=AWAY、10:00〜10:30）</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>request.breakKind="AWAY"、breakStart="10:00"、breakEnd="10:30"。correctedClockIn / Out・leaveTypeId・unit・days は null、applicantBalance=null、getRemainingDays は呼ばれない</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>HH:mm 形式の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>LEAVE / CLOCK_CORRECTION の申請</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>breakKind / breakStart / breakEnd が null</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>9.2 RequestController（MockMvc / API テスト）</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="10" t="n"/>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>観点・条件</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>期待結果</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>本人が GET /api/requests/{id}</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>200、request.requestId が一致</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>日時は +09:00 付き</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>GET /api/requests/abc</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>400 E-002「入力内容が正しくありません。」</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>500 にならないこと</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>他人の申請 ID</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>403 E-010</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Authorization なし</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>401 / E-001（AuthenticationEntryPoint の JSON）</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>9.3 結合テスト（実 DB）</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>観点・条件</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
         </is>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>GET /api/requests/abc</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>400 E-002「入力内容が正しくありません。」</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>500 にならないこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>他人の申請 ID</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>403 E-010</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Authorization なし</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>401 / E-001（AuthenticationEntryPoint の JSON）</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>取下げ済みの申請に GET</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>200、steps[].status=SKIPPED が JSON に出る（"WAITING" ではない）</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>結合</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>9.3 結合テスト（実 DB）</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>観点・条件</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>ONL-005 で提出 → ONL-007 で取得</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>steps 2件（1段目=上長 WAITING current=true）、currentStep=1</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>上長なしのケースは steps 1件・currentStep=2</t>
         </is>
@@ -1712,8 +1893,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A33:E33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1726,7 +1907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1811,6 +1992,29 @@
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="109" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正申請（BREAK_CORRECTION）と表示ステータス SKIPPED に対応：応答の request に breakKind / breakStart / breakEnd（HH:mm）を追加。steps[].status は、申請が PENDING でなく（取下げ・差戻し・却下）DB が WAITING のままのステップを表示専用の SKIPPED（画面は「処理なし」）として返す仕様（RequestService#displayStatus）を追記。current は従来どおり DB の status で判定（SKIPPED は false）。マッピング・方式・テスト観点を更新</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1824,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F43"/>
+  <dimension ref="A2:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1911,7 +2115,7 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="19" customHeight="1">
+    <row r="7" ht="49" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>目的</t>
@@ -1919,7 +2123,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>申請1件の内容、承認履歴（承認ステップ）、申請者の休暇残日数を返す。申請者の確認画面（SCR-106）と承認者の判断画面（SCR-202）で共用する。</t>
+          <t>申請1件の内容（休暇・打刻修正・休憩離席修正）、承認履歴（承認ステップ）、申請者の休暇残日数を返す。申請者の確認画面（SCR-106）と承認者の判断画面（SCR-202）で共用する。申請がすでに承認待ちでない（取下げ・差戻し・却下）のに未処理のまま残った承認ステップは、表示上の状態 SKIPPED（画面は「処理なし」）として返す（DB の値は変更しない）。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -2099,7 +2303,7 @@
       <c r="E18" s="9" t="n"/>
       <c r="F18" s="10" t="n"/>
     </row>
-    <row r="19" ht="19" customHeight="1">
+    <row r="19" ht="34" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>KF-BD-005</t>
@@ -2112,7 +2316,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>申請種別・申請状態・取得単位・承認ステップ状態・申請状態遷移</t>
+          <t>申請種別（LEAVE / CLOCK_CORRECTION / BREAK_CORRECTION）・申請状態・取得単位・承認ステップ状態（WAITING / APPROVED / RETURNED / REJECTED。応答では表示用に SKIPPED を追加）・申請状態遷移</t>
         </is>
       </c>
       <c r="D19" s="9" t="n"/>
@@ -2219,7 +2423,7 @@
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="10" t="n"/>
     </row>
-    <row r="25" ht="19" customHeight="1">
+    <row r="25" ht="34" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
           <t>KF-BD-SCR-106 / 202</t>
@@ -2232,7 +2436,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>承認履歴・申請者の残日数の表示項目</t>
+          <t>承認履歴・申請者の残日数の表示項目。ステップ SKIPPED は「処理なし」と表示。休憩・離席修正の項目（種別・修正後 開始/終了）</t>
         </is>
       </c>
       <c r="D25" s="9" t="n"/>
@@ -2299,436 +2503,476 @@
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="10" t="n"/>
     </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>1.3 対象クラス一覧（パッケージ：com.example.kintaiflow）</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>ONL-008</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>申請取下げ</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>取下げ後の WAITING ステップは本 API で SKIPPED として返る（displayStatus）</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>ONL-011 / ONL-012</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>申請差戻し／却下</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>差戻し・却下後に残る WAITING ステップも SKIPPED として返る</t>
+        </is>
+      </c>
       <c r="D30" s="9" t="n"/>
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="10" t="n"/>
     </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>1.3 対象クラス一覧（パッケージ：com.example.kintaiflow）</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>パッケージ</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>クラス名</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>責務</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>ファイル</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>新規/既存</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>controller</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>RequestController</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Controller</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>本処理は detail を追加</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>controller/RequestController.java</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>既存（ONL-005 で定義）。detail を追加</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>RequestService</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>本処理は getDetail / assertCanView / toDetail を追加</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>service/RequestService.java</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>既存（ONL-005 で定義）。getDetail を追加</t>
         </is>
       </c>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>service</t>
+          <t>controller</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>LeaveBalanceService</t>
+          <t>RequestController</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Controller</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>getRemainingDays で申請者の残日数を取得</t>
+          <t>本処理は detail を追加</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>service/LeaveBalanceService.java</t>
+          <t>controller/RequestController.java</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>既存（ONL-005 で定義）</t>
+          <t>既存（ONL-005 で定義）。detail を追加</t>
         </is>
       </c>
     </row>
     <row r="35" ht="49" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>repository</t>
+          <t>service</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>RequestRepository / ApprovalStepRepository</t>
+          <t>RequestService</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>申請・承認ステップの取得（findById / findByRequestIdOrderByStepNo）</t>
+          <t>本処理は getDetail / assertCanView / toDetail / toSteps / displayStatus を追加</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>repository/</t>
+          <t>service/RequestService.java</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>既存（ONL-005 で定義）</t>
+          <t>既存（ONL-005 で定義）。getDetail を追加</t>
         </is>
       </c>
     </row>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
+          <t>service</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>LeaveBalanceService</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>getRemainingDays で申請者の残日数を取得</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>service/LeaveBalanceService.java</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-005 で定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="49" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
           <t>repository</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>RequestRepository / ApprovalStepRepository</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>申請・承認ステップの取得（findById / findByRequestIdOrderByStepNo）</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>repository/</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-005 で定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>repository</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>UserRepository / LeaveTypeRepository</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>氏名・ロール・種別名の取得（findById / findAllById）</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>repository/</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001 / ONL-005）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>repository</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>DepartmentRepository</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Repository</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>部署名の取得（findById）</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>repository/DepartmentRepository.java</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>新規（最初の利用者。ONL-014 が拡張）</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="19" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>entity</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>departments のマッピング</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>entity/Department.java</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>新規（最初の利用者）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
+          <t>repository</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>DepartmentRepository</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>部署名の取得（findById）</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>repository/DepartmentRepository.java</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>新規（最初の利用者。ONL-014 が拡張）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>departments のマッピング</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>entity/Department.java</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>新規（最初の利用者）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Request / ApprovalStep / User / LeaveType</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>各テーブルのマッピング</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>entity/</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001 / ONL-005）</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="42" ht="94" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>dto</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>RequestDetailResponse / RequestDetail / StepDetail</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>DTO(record)</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>正常応答（申請内容・承認履歴・申請者残日数）</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>正常応答（申請内容・承認履歴・申請者残日数）。RequestDetail は休憩離席修正の breakKind / breakStart / breakEnd を含む。StepDetail.status は表示状態（SKIPPED を含む）</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>dto/</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="49" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="43" ht="49" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>AppTime</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Utility</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>日時の ISO 8601（+09:00）変換 AppTime.toIso を使用（定義は ONL-002）</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>config/AppTime.java</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-002 で定義）</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="64" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="44" ht="64" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>exception</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>GlobalExceptionHandler</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>ControllerAdvice</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>handleTypeMismatch（パス変数が数値でない場合の 400 / E-002）を使用。定義は ONL-001 の共通基盤への追加改修</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>exception/GlobalExceptionHandler.java</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001 で定義）。本処理での追記なし</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>exception</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>BusinessException / ErrorResponse</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>共通部品</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>業務エラー・共通エラー応答</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>exception/・dto/</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="29">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C17:F17"/>
@@ -2741,15 +2985,17 @@
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="C30:F30"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C25:F25"/>
-    <mergeCell ref="A30:F30"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="B6:F6"/>
@@ -2846,7 +3092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F37"/>
+  <dimension ref="A2:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3064,7 +3310,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>LEAVE / CLOCK_CORRECTION</t>
+          <t>LEAVE / CLOCK_CORRECTION / BREAK_CORRECTION</t>
         </is>
       </c>
       <c r="E13" s="9" t="n"/>
@@ -3136,7 +3382,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>打刻修正は null</t>
+          <t>休暇のみ。打刻修正・休憩離席修正は null</t>
         </is>
       </c>
       <c r="E16" s="9" t="n"/>
@@ -3160,7 +3406,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>yyyy-MM-dd（打刻修正は対象日・同値）</t>
+          <t>yyyy-MM-dd（打刻修正・休憩離席修正は対象日・同値）</t>
         </is>
       </c>
       <c r="E17" s="9" t="n"/>
@@ -3184,7 +3430,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>FULL / AM / PM、小数1桁。打刻修正は null</t>
+          <t>FULL / AM / PM、小数1桁。打刻修正・休憩離席修正は null</t>
         </is>
       </c>
       <c r="E18" s="9" t="n"/>
@@ -3208,21 +3454,21 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>HH:mm。休暇は null</t>
+          <t>HH:mm。休暇・休憩離席修正は null</t>
         </is>
       </c>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="10" t="n"/>
     </row>
-    <row r="20" ht="19" customHeight="1">
+    <row r="20" ht="34" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>request.reason</t>
+          <t>request.breakKind</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>理由</t>
+          <t>休憩・離席の種別</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -3232,7 +3478,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>null 可</t>
+          <t>BREAK_CORRECTION のみ。BREAK（休憩）／ AWAY（日中離席）。それ以外は null（requests.corrected_break_kind）</t>
         </is>
       </c>
       <c r="E20" s="9" t="n"/>
@@ -3241,36 +3487,36 @@
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>request.status / currentStep</t>
+          <t>request.breakStart / breakEnd</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>申請状態・現在の承認段</t>
+          <t>修正後の区間の開始・終了時刻</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>String / Integer</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>6値、0〜2</t>
+          <t>HH:mm（対象日の時刻）。BREAK_CORRECTION のみ、それ以外は null（requests.corrected_break_start / end の時刻部分）</t>
         </is>
       </c>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="10" t="n"/>
     </row>
-    <row r="22" ht="34" customHeight="1">
+    <row r="22" ht="19" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>request.submittedAt / createdAt</t>
+          <t>request.reason</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>提出日時・作成日時</t>
+          <t>理由</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
@@ -3280,7 +3526,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>ISO 8601（+09:00 付き）。submittedAt は下書きで null</t>
+          <t>null 可</t>
         </is>
       </c>
       <c r="E22" s="9" t="n"/>
@@ -3289,22 +3535,22 @@
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>steps</t>
+          <t>request.status / currentStep</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>承認履歴</t>
+          <t>申請状態・現在の承認段</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>List&lt;StepDetail&gt;</t>
+          <t>String / Integer</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>step_no 昇順。下書きは空配列</t>
+          <t>6値、0〜2</t>
         </is>
       </c>
       <c r="E23" s="9" t="n"/>
@@ -3313,118 +3559,118 @@
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>steps[].stepNo / stepName</t>
+          <t>request.submittedAt / createdAt</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>段・段名</t>
+          <t>提出日時・作成日時</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Integer / String</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>1:上長、2:管理者</t>
+          <t>ISO 8601（+09:00 付き）。submittedAt は下書きで null</t>
         </is>
       </c>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="10" t="n"/>
     </row>
-    <row r="25" ht="49" customHeight="1">
+    <row r="25" ht="34" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>steps[].approverId / approverName</t>
+          <t>steps</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>承認者ID・氏名</t>
+          <t>承認履歴</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Long / String</t>
+          <t>List&lt;StepDetail&gt;</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>未設定（2段目の処理前）は null</t>
+          <t>step_no 昇順。下書きは空配列</t>
         </is>
       </c>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="10" t="n"/>
     </row>
-    <row r="26" ht="19" customHeight="1">
+    <row r="26" ht="34" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>steps[].status</t>
+          <t>steps[].stepNo / stepName</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>ステップ状態</t>
+          <t>段・段名</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Integer / String</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>WAITING / APPROVED / RETURNED / REJECTED（DB の値そのまま）</t>
+          <t>1:上長、2:管理者</t>
         </is>
       </c>
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="10" t="n"/>
     </row>
-    <row r="27" ht="34" customHeight="1">
+    <row r="27" ht="49" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>steps[].comment / actedAt</t>
+          <t>steps[].approverId / approverName</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>コメント・処理日時</t>
+          <t>承認者ID・氏名</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long / String</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>未処理は null。actedAt は ISO 8601</t>
+          <t>未設定（2段目の処理前）は null</t>
         </is>
       </c>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="10" t="n"/>
     </row>
-    <row r="28" ht="34" customHeight="1">
+    <row r="28" ht="64" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>steps[].current</t>
+          <t>steps[].status</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>現在の処理待ちか</t>
+          <t>ステップの表示状態</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>申請が PENDING かつ stepNo = currentStep かつ status = WAITING のとき true（取下げ後の WAITING は false）</t>
+          <t>WAITING / APPROVED / RETURNED / REJECTED / SKIPPED。DB の値をそのまま返すが、申請が PENDING でなく（取下げ WITHDRAWN・差戻し RETURNED・却下 REJECTED）かつステップが WAITING のままのものは SKIPPED（処理なし）。DB の approval_steps.status は WAITING のまま変更しない</t>
         </is>
       </c>
       <c r="E28" s="9" t="n"/>
@@ -3433,34 +3679,82 @@
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>applicantBalance</t>
+          <t>steps[].comment / actedAt</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>申請者の休暇残日数</t>
+          <t>コメント・処理日時</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Decimal</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>LEAVE かつ種別が LIMITED のときのみ（小数1桁）。それ以外は null</t>
+          <t>未処理は null。actedAt は ISO 8601</t>
         </is>
       </c>
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="10" t="n"/>
     </row>
-    <row r="30" ht="274" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>steps[].current</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>現在の処理待ちか</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>申請が PENDING かつ stepNo = currentStep かつ DB の status = WAITING のとき true（SKIPPED は false）</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>applicantBalance</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>申請者の休暇残日数</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>LEAVE かつ種別が LIMITED のときのみ（小数1桁）。それ以外は null</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="484" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>レスポンス例</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>{
   "request": {
@@ -3468,7 +3762,8 @@
     "applicantId": 3, "applicantName": "山田 太郎", "departmentName": "営業部",
     "leaveTypeId": 1, "leaveTypeName": "年次有給休暇",
     "startDate": "2026-10-14", "endDate": "2026-10-16", "unit": "FULL", "days": 3.0,
-    "correctedClockIn": null, "correctedClockOut": null, "reason": "私用のため",
+    "correctedClockIn": null, "correctedClockOut": null,
+    "breakKind": null, "breakStart": null, "breakEnd": null, "reason": "私用のため",
     "status": "PENDING", "currentStep": 2,
     "submittedAt": "2026-10-02T10:15:30+09:00", "createdAt": "2026-10-02T10:15:30+09:00"
   },
@@ -3479,93 +3774,55 @@
       "status": "WAITING", "comment": null, "actedAt": null, "current": true }
   ],
   "applicantBalance": 12.0
+}
+■休憩・離席修正申請（BREAK_CORRECTION）で取下げ済みの例（2段目は WAITING のまま取下げ → SKIPPED）
+{
+  "request": { "requestId": 21, "requestType": "BREAK_CORRECTION", "startDate": "2026-10-01", "endDate": "2026-10-01",
+    "breakKind": "BREAK", "breakStart": "12:00", "breakEnd": "13:00", "status": "WITHDRAWN", "currentStep": 1, ... },
+  "steps": [
+    { "stepNo": 1, "stepName": "上長", "status": "SKIPPED", "current": false, ... },
+    { "stepNo": 2, "stepName": "管理者", "status": "SKIPPED", "current": false, ... }
+  ],
+  "applicantBalance": null
 }</t>
         </is>
       </c>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="10" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>4.3 レスポンス（エラー）  共通形式 ErrorResponse</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="n"/>
       <c r="C32" s="9" t="n"/>
       <c r="D32" s="9" t="n"/>
       <c r="E32" s="9" t="n"/>
       <c r="F32" s="10" t="n"/>
     </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>項目名</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>論理名</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="10" t="n"/>
-    </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>エラーコード</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>E-xxx（8. エラー一覧）</t>
-        </is>
-      </c>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>4.3 レスポンス（エラー）  共通形式 ErrorResponse</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="10" t="n"/>
     </row>
     <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>メッセージ</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>画面に表示する文言（日本語）</t>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>項目名</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>論理名</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>内容</t>
         </is>
       </c>
       <c r="E35" s="9" t="n"/>
@@ -3574,34 +3831,82 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>fieldErrors</t>
+          <t>code</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>項目別エラー</t>
+          <t>エラーコード</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>[{field, message}]。入力チェックエラー時のみ要素あり、それ以外は空配列</t>
+          <t>E-xxx（8. エラー一覧）</t>
         </is>
       </c>
       <c r="E36" s="9" t="n"/>
       <c r="F36" s="10" t="n"/>
     </row>
-    <row r="37" ht="79" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>メッセージ</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>画面に表示する文言（日本語）</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>fieldErrors</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>項目別エラー</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>[{field, message}]。入力チェックエラー時のみ要素あり、それ以外は空配列</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="10" t="n"/>
+    </row>
+    <row r="39" ht="79" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>エラー例</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>HTTP 403
 { "code": "E-010", "message": "この操作を行う権限がありません。", "fieldErrors": [] }
@@ -3609,13 +3914,13 @@
 { "code": "E-002", "message": "入力内容が正しくありません。", "fieldErrors": [] }</t>
         </is>
       </c>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="10" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="33">
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D27:F27"/>
@@ -3624,26 +3929,28 @@
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D28:F28"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A32:F32"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D30:F30"/>
     <mergeCell ref="D25:F25"/>
     <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D33:F33"/>
     <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D38:F38"/>
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="D23:F23"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="D35:F35"/>
-    <mergeCell ref="B37:F37"/>
     <mergeCell ref="D26:F26"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D34:F34"/>
     <mergeCell ref="D10:F10"/>
-    <mergeCell ref="B30:F30"/>
     <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D31:F31"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="D36:F36"/>
     <mergeCell ref="D21:F21"/>
@@ -3850,7 +4157,7 @@
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10" t="n"/>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="94" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>⑥</t>
@@ -3858,12 +4165,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>レスポンス返却</t>
+          <t>応答を組み立てて返却</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>RequestDetailResponse {request, steps, applicantBalance}</t>
+          <t>RequestDetailResponse {request, steps, applicantBalance}。toDetail が休憩離席修正の breakKind / breakStart / breakEnd（HH:mm）を含め、toSteps が各ステップの status を displayStatus で決定（申請が PENDING でなく DB が WAITING のステップは SKIPPED）し、current を算出</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -3911,7 +4218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F71"/>
+  <dimension ref="A2:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4644,7 +4951,7 @@
       <c r="E46" s="9" t="n"/>
       <c r="F46" s="10" t="n"/>
     </row>
-    <row r="47" ht="34" customHeight="1">
+    <row r="47" ht="64" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
           <t>シグネチャ</t>
@@ -4653,7 +4960,9 @@
       <c r="B47" s="12" t="inlineStr">
         <is>
           <t>private RequestDetail toDetail(Request r, User applicant, String dept, LeaveType type)
-private List&lt;StepDetail&gt; toSteps(Request r, List&lt;ApprovalStep&gt; steps, Map&lt;Long, User&gt; users)</t>
+private List&lt;StepDetail&gt; toSteps(Request r, List&lt;ApprovalStep&gt; steps, Map&lt;Long, User&gt; users)
+private static String displayStatus(Request r, ApprovalStep s)
+private static String formatTime(LocalDateTime t)</t>
         </is>
       </c>
       <c r="C47" s="9" t="n"/>
@@ -4669,7 +4978,7 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Entity を応答 DTO に変換する。</t>
+          <t>Entity を応答 DTO に変換する。承認ステップの状態は displayStatus で表示用に決める（DB の値は変更しない）。</t>
         </is>
       </c>
       <c r="C48" s="9" t="n"/>
@@ -4785,7 +5094,7 @@
       <c r="E54" s="9" t="n"/>
       <c r="F54" s="10" t="n"/>
     </row>
-    <row r="55" ht="154" customHeight="1">
+    <row r="55" ht="349" customHeight="1">
       <c r="A55" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -4793,15 +5102,27 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>toDetail: applicantName = applicant == null ? null : applicant.getName();  leaveTypeName = type == null ? null : type.getName();
-   correctedClockIn  = t == null ? null : t.toLocalTime().format(DateTimeFormatter.ofPattern("HH:mm"));（Out も同様）
-   submittedAt / createdAt = AppTime.toIso(r.getSubmittedAt()) / AppTime.toIso(r.getCreatedAt())（共通ユーティリティ。ONL-002 で定義）
-toSteps: 各 s について
-   stepName   = s.getStepNo() == 1 ? "上長" : "管理者"
+          <t>// toDetail
+return new RequestDetail(r.getId(), r.getRequestType(), r.getUserId(),
+    applicant == null ? null : applicant.getName(), dept,
+    r.getLeaveTypeId(), type == null ? null : type.getName(),
+    r.getStartDate(), r.getEndDate(), r.getUnit(), r.getDays(),
+    formatTime(r.getCorrectedClockIn()), formatTime(r.getCorrectedClockOut()),                       // HH:mm
+    r.getCorrectedBreakKind(), formatTime(r.getCorrectedBreakStart()), formatTime(r.getCorrectedBreakEnd()),   // 休憩離席修正
+    r.getReason(), r.getStatus(), r.getCurrentStep(),
+    AppTime.toIso(r.getSubmittedAt()), AppTime.toIso(r.getCreatedAt()));
+// formatTime(t): t == null ? null : t.format(DateTimeFormatter.ofPattern("HH:mm"))
+// toSteps: 各 s について
+   stepName     = s.getStepNo() == 1 ? "上長" : "管理者"
    approverName = users.get(s.getApproverId())?.getName()（approverId が null なら null）
-   actedAt    = AppTime.toIso(s.getActedAt())
-   current    = RequestStatus.PENDING.equals(r.getStatus()) &amp;&amp; s.getStepNo().equals(r.getCurrentStep())
-                &amp;&amp; StepStatus.WAITING.equals(s.getStatus())</t>
+   status       = displayStatus(r, s)
+   actedAt      = AppTime.toIso(s.getActedAt())
+   current      = RequestStatus.PENDING.equals(r.getStatus()) &amp;&amp; s.getStepNo().equals(r.getCurrentStep())
+                  &amp;&amp; StepStatus.WAITING.equals(s.getStatus())      // DB の status で判定（表示状態ではない）
+// displayStatus
+if (StepStatus.WAITING.equals(s.getStatus()) &amp;&amp; !RequestStatus.PENDING.equals(r.getStatus()))
+    return "SKIPPED";            // 申請が取下げ・差戻し・却下で打ち切られたのに未処理のまま残ったステップ
+return s.getStatus();</t>
         </is>
       </c>
       <c r="C55" s="9" t="n"/>
@@ -4817,7 +5138,7 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>AppTime#toIso（ONL-002 で定義）</t>
+          <t>AppTime#toIso（ONL-002 で定義）/ displayStatus / formatTime</t>
         </is>
       </c>
       <c r="C56" s="9" t="n"/>
@@ -4825,7 +5146,7 @@
       <c r="E56" s="9" t="n"/>
       <c r="F56" s="10" t="n"/>
     </row>
-    <row r="57" ht="49" customHeight="1">
+    <row r="57" ht="124" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -4833,7 +5154,9 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>状態を WITHDRAWN にした申請の WAITING ステップは DB 上は WAITING のままだが current=false となり、画面は「無効」として扱える（ONL-008）。
+          <t>【SKIPPED】approval_steps.status は WAITING / APPROVED / RETURNED / REJECTED の 4 値で、SKIPPED は DB に存在しない表示専用の値。申請が PENDING でないのに WAITING のままのステップ（取下げ WITHDRAWN の全 WAITING ステップ、1 段目の差戻し RETURNED・却下 REJECTED の後に残る 2 段目 など）を、画面が「承認待ち」と誤解しないよう SKIPPED（画面は「処理なし」）に置き換えて返す。DB の値は変えない（取下げ・差戻し・却下の各処理でもステップは更新しない）。差戻し後の再提出（ONL-022）では旧ステップが全削除されて作り直される。
+【current】current は DB の status = WAITING を基準に計算するため SKIPPED は常に false（申請が PENDING のときだけ true がありうる）。displayStatus と current の判定基準を取り違えないこと。
+【休憩離席修正】breakKind は BREAK / AWAY の文字列、breakStart / breakEnd は対象日の HH:mm。BREAK_CORRECTION 以外は null。
 日時変換は RequestService のメソッドではなく AppTime#toIso（config/AppTime.java）。ONL-006 の toSummary と同じ変換。</t>
         </is>
       </c>
@@ -5050,7 +5373,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="49" customHeight="1">
+    <row r="69" ht="94" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
           <t>D-5</t>
@@ -5063,14 +5386,14 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>申請が PENDING かつ段が現在段かつ WAITING のとき true を追加提供</t>
+          <t>申請が PENDING かつ段が現在段かつ（DB 上の）WAITING のとき true を追加提供。あわせて steps[].status は、申請が PENDING でなく DB が WAITING のステップを SKIPPED（処理なし）として返す</t>
         </is>
       </c>
       <c r="D69" s="9" t="n"/>
       <c r="E69" s="10" t="n"/>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>取下げ後の WAITING を画面が誤って「承認待ち」と表示しないため（KF-DD-002 の steps[] に項目追加）</t>
+          <t>取下げ・差戻し・却下後の WAITING を画面が誤って「承認待ち」と表示しないため（KF-DD-002 の steps[] に項目追加）。SKIPPED は表示専用で DB には保存しない（RequestService#displayStatus）</t>
         </is>
       </c>
     </row>
@@ -5122,8 +5445,32 @@
         </is>
       </c>
     </row>
+    <row r="72" ht="79" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正申請の表示</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>RequestDetail に breakKind / breakStart / breakEnd（HH:mm）を追加。BREAK_CORRECTION 以外は null</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>画面（SCR-106 / 202）が種別・修正後 開始・修正後 終了を表示するため（requests.corrected_break_*）。休憩離席修正は days / unit / leaveType を持たない</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="63">
+  <mergeCells count="64">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="C52:F52"/>
@@ -5157,6 +5504,7 @@
     <mergeCell ref="B57:F57"/>
     <mergeCell ref="C67:E67"/>
     <mergeCell ref="B53:F53"/>
+    <mergeCell ref="C72:E72"/>
     <mergeCell ref="A63:F63"/>
     <mergeCell ref="C66:E66"/>
     <mergeCell ref="B34:F34"/>
@@ -5199,7 +5547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F83"/>
+  <dimension ref="A2:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5330,7 +5678,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="19" customHeight="1">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>request_type</t>
@@ -5358,7 +5706,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>LEAVE / CLOCK_CORRECTION（ck_req_type）</t>
+          <t>LEAVE / CLOCK_CORRECTION / BREAK_CORRECTION（ck_req_type）</t>
         </is>
       </c>
     </row>
@@ -5422,11 +5770,11 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>休暇の開始日／打刻修正の対象日</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="19" customHeight="1">
+          <t>休暇の開始日／打刻修正・休憩離席修正の対象日</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>end_date</t>
@@ -5454,7 +5802,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>休暇の終了日／打刻修正は startDate と同値</t>
+          <t>休暇の終了日／打刻修正・休憩離席修正は startDate と同値</t>
         </is>
       </c>
     </row>
@@ -5586,15 +5934,15 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="19" customHeight="1">
+    <row r="15" ht="34" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>corrected_break_kind</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>correctedBreakKind</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -5609,93 +5957,93 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>○ 出力</t>
+          <t>○ 出力（breakKind）</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
+          <t>BREAK / AWAY（ck_req_break_kind）。BREAK_CORRECTION のみ</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>corrected_break_start</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>correctedBreakStart</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>LocalDateTime</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>○ 閲覧判定（DRAFT）・current 判定・出力</t>
+          <t>○ 出力（breakStart。HH:mm）</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>DRAFT / PENDING / RETURNED / REJECTED / APPROVED / WITHDRAWN（ck_req_status）</t>
+          <t>修正後の区間の開始日時（JST）。BREAK_CORRECTION のみ</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>current_step</t>
+          <t>corrected_break_end</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>currentStep</t>
+          <t>correctedBreakEnd</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>LocalDateTime</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>○ current 判定・出力</t>
+          <t>○ 出力（breakEnd。HH:mm）</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>現在の承認段。DRAFT は 0、提出後は 1 または 2</t>
+          <t>修正後の区間の終了日時（JST）。BREAK_CORRECTION のみ</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>submitted_at</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>submittedAt</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>LocalDateTime</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -5710,688 +6058,688 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>提出日時（JST）。DRAFT は NULL</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>○ 閲覧判定（DRAFT）・current 判定・出力</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>DRAFT / PENDING / RETURNED / REJECTED / APPROVED / WITHDRAWN（ck_req_status）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>current_step</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>currentStep</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>○ current 判定・出力</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>現在の承認段。DRAFT は 0、提出後は 1 または 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>submitted_at</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>submittedAt</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>○ 出力</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>提出日時（JST）。DRAFT は NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>○ 出力</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="64" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_requests_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>■ approval_steps</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>○ 出力</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>IDENTITY 自動採番</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="27" ht="19" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>requestId</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>○ 検索条件</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>FK requests。UNIQUE(request_id, step_no)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>step_no</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>stepNo</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>○ 出力</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>1:上長 / 2:管理者（ck_as_step）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>approver_id</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>approverId</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>○ 閲覧判定・承認者名の取得キー</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>FK users。1段目は作成時に上長を設定、2段目は処理時に設定（作成時は NULL）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>○ 出力</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>WAITING / APPROVED / RETURNED / REJECTED（ck_as_status）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
+          <t>step_no</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>stepNo</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>○ 出力</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>1:上長 / 2:管理者（ck_as_step）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>approver_id</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>approverId</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>○ 閲覧判定・承認者名の取得キー</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>FK users。1段目は作成時に上長を設定、2段目は処理時に設定（作成時は NULL）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="49" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>○ 出力（表示状態に変換）・current 判定（DB の値）</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>WAITING / APPROVED / RETURNED / REJECTED（ck_as_status）。応答では申請が PENDING でない WAITING を SKIPPED に置換（DB 不変）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>○ 出力</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>VARCHAR(500)。承認者のコメント</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>acted_at</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>actedAt</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>○ 出力</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>処理日時（JST）</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="64" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_approval_steps_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>■ users</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="10" t="n"/>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>○ 検索条件（IN）</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>IDENTITY 自動採番</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>UNIQUE（uq_users_1）、VARCHAR(255)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>password_hash</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>passwordHash</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>BCrypt ハッシュ。VARCHAR(255)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>○ 出力（申請者名・承認者名）</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="34" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>○ ADMIN 判定（閲覧者）</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>EMPLOYEE / MANAGER / ADMIN</t>
         </is>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>department_id</t>
+          <t>password_hash</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>departmentId</t>
+          <t>passwordHash</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>○ 部署名の取得キー</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>FK departments</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="19" customHeight="1">
+          <t>BCrypt ハッシュ。VARCHAR(255)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>manager_id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>managerId</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>○ 出力（申請者名・承認者名）</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>FK users（自己参照）。1段目承認者の決定に使用</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="19" customHeight="1">
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>hire_date</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>hireDate</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>LocalDate</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -6401,433 +6749,433 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr"/>
+          <t>○ ADMIN 判定（閲覧者）</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>EMPLOYEE / MANAGER / ADMIN</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
+          <t>department_id</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>departmentId</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>○ 部署名の取得キー</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>FK departments</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>manager_id</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>managerId</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>FK users（自己参照）。1段目承認者の決定に使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>hire_date</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>hireDate</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>LocalDate</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>ACTIVE / INACTIVE（既定 ACTIVE）</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="64" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="47" ht="64" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_users_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>■ departments</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n"/>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="10" t="n"/>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="10" t="n"/>
+    </row>
+    <row r="49" ht="19" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="50" ht="19" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>○ 検索条件</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>IDENTITY 自動採番</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>○ 出力（departmentName）</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="64" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+    <row r="53" ht="64" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_departments_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>■ leave_types</t>
         </is>
       </c>
-      <c r="B51" s="9" t="n"/>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
-      <c r="E51" s="9" t="n"/>
-      <c r="F51" s="10" t="n"/>
-    </row>
-    <row r="52" ht="19" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="10" t="n"/>
+    </row>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>○ 検索条件</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>IDENTITY 自動採番</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>○ 出力（leaveTypeName）</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>UNIQUE（uq_leave_types_1）、VARCHAR(100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>legal_basis</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>legalBasis</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
         </is>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>is_paid</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>isPaid</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -6837,20 +7185,24 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="inlineStr"/>
+          <t>○ 検索条件</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>IDENTITY 自動採番</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="34" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>max_days_rule</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>maxDaysRule</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -6860,39 +7212,39 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>○ applicantBalance 要否</t>
+          <t>○ 出力（leaveTypeName）</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>LIMITED（残日数の範囲内でのみ取得可）／ UNLIMITED（ck_lt_rule）</t>
+          <t>UNIQUE（uq_leave_types_1）、VARCHAR(100)</t>
         </is>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>allow_half_day</t>
+          <t>legal_basis</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>allowHalfDay</t>
+          <t>legalBasis</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -6902,19 +7254,19 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>false の種別は FULL のみ指定可</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>is_paid</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>isPaid</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -6932,230 +7284,226 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>既定 TRUE。false の種別は申請不可</t>
-        </is>
-      </c>
+      <c r="F59" s="7" t="inlineStr"/>
     </row>
     <row r="60" ht="34" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
+          <t>max_days_rule</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>maxDaysRule</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>○ applicantBalance 要否</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>LIMITED（残日数の範囲内でのみ取得可）／ UNLIMITED（ck_lt_rule）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>allow_half_day</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>allowHalfDay</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>false の種別は FULL のみ指定可</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="19" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>is_active</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>isActive</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>既定 TRUE。false の種別は申請不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="64" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
+    <row r="64" ht="64" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_leave_types_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="19" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
+    <row r="65" ht="19" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>■ leave_balances</t>
         </is>
       </c>
-      <c r="B62" s="9" t="n"/>
-      <c r="C62" s="9" t="n"/>
-      <c r="D62" s="9" t="n"/>
-      <c r="E62" s="9" t="n"/>
-      <c r="F62" s="10" t="n"/>
-    </row>
-    <row r="63" ht="19" customHeight="1">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="B65" s="9" t="n"/>
+      <c r="C65" s="9" t="n"/>
+      <c r="D65" s="9" t="n"/>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="10" t="n"/>
+    </row>
+    <row r="66" ht="19" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="19" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>IDENTITY 自動採番</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="19" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>userId</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>○ 集計条件</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>FK users</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="19" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>leave_type_id</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>leaveTypeId</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>○ 集計条件</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>FK leave_types</t>
         </is>
       </c>
     </row>
     <row r="67" ht="19" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>granted_days</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>grantedDays</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>BigDecimal</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -7165,29 +7513,29 @@
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>○ 残日数集計</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>DECIMAL(4,1)。付与日数</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="34" customHeight="1">
+          <t>IDENTITY 自動採番</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="19" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>used_days</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>usedDays</t>
+          <t>userId</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>BigDecimal</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -7197,29 +7545,29 @@
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>○ 残日数集計</t>
+          <t>○ 集計条件</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>DECIMAL(4,1)。既定 0。消化は ONL-010（承認）で加算</t>
+          <t>FK users</t>
         </is>
       </c>
     </row>
     <row r="69" ht="19" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>granted_on</t>
+          <t>leave_type_id</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>grantedOn</t>
+          <t>leaveTypeId</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>LocalDate</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -7229,25 +7577,29 @@
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr"/>
-    </row>
-    <row r="70" ht="34" customHeight="1">
+          <t>○ 集計条件</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>FK leave_types</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="19" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>expires_on</t>
+          <t>granted_days</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>expiresOn</t>
+          <t>grantedDays</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>LocalDate</t>
+          <t>BigDecimal</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -7257,135 +7609,178 @@
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>○ 失効判定（≧ 本日）</t>
+          <t>○ 残日数集計</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>失効日（付与日＋2年）。この日までは使用可</t>
+          <t>DECIMAL(4,1)。付与日数</t>
         </is>
       </c>
     </row>
     <row r="71" ht="34" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
+          <t>used_days</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>usedDays</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>BigDecimal</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>○ 残日数集計</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>DECIMAL(4,1)。既定 0。消化は ONL-010（承認）で加算</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="19" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>granted_on</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>grantedOn</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>LocalDate</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73" ht="34" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>expires_on</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>expiresOn</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>LocalDate</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>○ 失効判定（≧ 本日）</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>失効日（付与日＋2年）。この日までは使用可</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="34" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
+      <c r="F74" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="64" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
+    <row r="75" ht="64" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_leave_balances_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>7.2 SQL・クエリ</t>
         </is>
       </c>
-      <c r="B74" s="9" t="n"/>
-      <c r="C74" s="9" t="n"/>
-      <c r="D74" s="9" t="n"/>
-      <c r="E74" s="9" t="n"/>
-      <c r="F74" s="10" t="n"/>
-    </row>
-    <row r="75" ht="34" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>申請の取得（RequestRepository#findById）</t>
-        </is>
-      </c>
-      <c r="B75" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM requests WHERE id = ?</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="n"/>
-      <c r="D75" s="9" t="n"/>
-      <c r="E75" s="9" t="n"/>
-      <c r="F75" s="10" t="n"/>
-    </row>
-    <row r="76" ht="64" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>承認ステップの取得（ApprovalStepRepository#findByRequestIdOrderByStepNo）</t>
-        </is>
-      </c>
-      <c r="B76" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM approval_steps WHERE request_id = ? ORDER BY step_no ASC</t>
-        </is>
-      </c>
-      <c r="C76" s="9" t="n"/>
-      <c r="D76" s="9" t="n"/>
-      <c r="E76" s="9" t="n"/>
-      <c r="F76" s="10" t="n"/>
-    </row>
-    <row r="77" ht="64" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>閲覧者・申請者・承認者（UserRepository#findById / findAllById）</t>
-        </is>
-      </c>
-      <c r="B77" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM users WHERE id = ?
-SELECT * FROM users WHERE id IN (?, ?, ?)</t>
-        </is>
-      </c>
+      <c r="B77" s="9" t="n"/>
       <c r="C77" s="9" t="n"/>
       <c r="D77" s="9" t="n"/>
       <c r="E77" s="9" t="n"/>
@@ -7394,13 +7789,12 @@
     <row r="78" ht="34" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>部署・休暇種別</t>
+          <t>申請の取得（RequestRepository#findById）</t>
         </is>
       </c>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>SELECT * FROM departments WHERE id = ?
-SELECT * FROM leave_types WHERE id = ?</t>
+          <t>SELECT * FROM requests WHERE id = ?</t>
         </is>
       </c>
       <c r="C78" s="9" t="n"/>
@@ -7408,16 +7802,15 @@
       <c r="E78" s="9" t="n"/>
       <c r="F78" s="10" t="n"/>
     </row>
-    <row r="79" ht="49" customHeight="1">
+    <row r="79" ht="64" customHeight="1">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>残日数合計（LeaveBalanceRepository#sumRemainingDays）</t>
+          <t>承認ステップの取得（ApprovalStepRepository#findByRequestIdOrderByStepNo）</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>SELECT SUM(granted_days - used_days) FROM leave_balances
- WHERE user_id = ? AND leave_type_id = ? AND expires_on &gt;= ?</t>
+          <t>SELECT * FROM approval_steps WHERE request_id = ? ORDER BY step_no ASC</t>
         </is>
       </c>
       <c r="C79" s="9" t="n"/>
@@ -7425,86 +7818,137 @@
       <c r="E79" s="9" t="n"/>
       <c r="F79" s="10" t="n"/>
     </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>7.3 設定値</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="n"/>
+    <row r="80" ht="64" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>閲覧者・申請者・承認者（UserRepository#findById / findAllById）</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE id = ?
+SELECT * FROM users WHERE id IN (?, ?, ?)</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="n"/>
+      <c r="D80" s="9" t="n"/>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="10" t="n"/>
+    </row>
+    <row r="81" ht="34" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>部署・休暇種別</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM departments WHERE id = ?
+SELECT * FROM leave_types WHERE id = ?</t>
+        </is>
+      </c>
       <c r="C81" s="9" t="n"/>
       <c r="D81" s="9" t="n"/>
       <c r="E81" s="9" t="n"/>
       <c r="F81" s="10" t="n"/>
     </row>
-    <row r="82" ht="19" customHeight="1">
-      <c r="A82" s="6" t="inlineStr">
+    <row r="82" ht="49" customHeight="1">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>残日数合計（LeaveBalanceRepository#sumRemainingDays）</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>SELECT SUM(granted_days - used_days) FROM leave_balances
+ WHERE user_id = ? AND leave_type_id = ? AND expires_on &gt;= ?</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="n"/>
+      <c r="D82" s="9" t="n"/>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="10" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>7.3 設定値</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="n"/>
+      <c r="C84" s="9" t="n"/>
+      <c r="D84" s="9" t="n"/>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="10" t="n"/>
+    </row>
+    <row r="85" ht="19" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>キー</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>格納場所</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n"/>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="F82" s="10" t="n"/>
-    </row>
-    <row r="83" ht="49" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
+      <c r="F85" s="10" t="n"/>
+    </row>
+    <row r="86" ht="49" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>spring.jpa.properties.hibernate.jdbc.time_zone</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>application.properties</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>Asia/Tokyo。日時の読み取りを JST に固定</t>
         </is>
       </c>
-      <c r="D83" s="10" t="n"/>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="D86" s="10" t="n"/>
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>ONL-005 と共通</t>
         </is>
       </c>
-      <c r="F83" s="10" t="n"/>
+      <c r="F86" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="A84:F84"/>
     <mergeCell ref="B78:F78"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="B76:F76"/>
-    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="B79:F79"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A65:F65"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
